--- a/datasets/agenda_implementation/data/output/evaluations.xlsx
+++ b/datasets/agenda_implementation/data/output/evaluations.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>fitness_check</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -505,7 +505,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>fitness_check</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -532,7 +532,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>fitness_check</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -559,7 +559,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>fitness_check</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>interim_evaluation</t>
+          <t>evaluation</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>interim_evaluation</t>
+          <t>evaluation</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>interim_evaluation</t>
+          <t>evaluation</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>interim_evaluation</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>interim_evaluation</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>interim_evaluation</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>interim_evaluation</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>interim_evaluation</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>interim_evaluation</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>interim_evaluation</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>interim_evaluation</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>interim_evaluation</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>interim_evaluation</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>interim_evaluation</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>

--- a/datasets/agenda_implementation/data/output/evaluations.xlsx
+++ b/datasets/agenda_implementation/data/output/evaluations.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AI0050</t>
+          <t>AI0053</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AI0051</t>
+          <t>AI0054</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AI0052</t>
+          <t>AI0055</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AI0053</t>
+          <t>AI0056</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AI0054</t>
+          <t>AI0057</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AI0055</t>
+          <t>AI0058</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AI0056</t>
+          <t>AI0059</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AI0057</t>
+          <t>AI0060</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AI0058</t>
+          <t>AI0061</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AI0059</t>
+          <t>AI0062</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AI0060</t>
+          <t>AI0063</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AI0061</t>
+          <t>AI0064</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AI0062</t>
+          <t>AI0065</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AI0063</t>
+          <t>AI0066</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AI0064</t>
+          <t>AI0067</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AI0065</t>
+          <t>AI0068</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AI0066</t>
+          <t>AI0069</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AI0067</t>
+          <t>AI0070</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AI0068</t>
+          <t>AI0071</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AI0069</t>
+          <t>AI0072</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AI0070</t>
+          <t>AI0073</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AI0071</t>
+          <t>AI0074</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AI0072</t>
+          <t>AI0075</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AI0073</t>
+          <t>AI0076</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>interim_evaluation</t>
+          <t>evaluation</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AI0074</t>
+          <t>AI0077</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>interim_evaluation</t>
+          <t>evaluation</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AI0075</t>
+          <t>AI0078</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>interim_evaluation</t>
+          <t>evaluation</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AI0076</t>
+          <t>AI0079</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>interim_evaluation</t>
+          <t>evaluation</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AI0077</t>
+          <t>AI0080</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>interim_evaluation</t>
+          <t>evaluation</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AI0078</t>
+          <t>AI0081</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>interim_evaluation</t>
+          <t>evaluation</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AI0079</t>
+          <t>AI0082</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>interim_evaluation</t>
+          <t>evaluation</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AI0080</t>
+          <t>AI0083</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AI0081</t>
+          <t>AI0084</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AI0082</t>
+          <t>AI0085</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AI0083</t>
+          <t>AI0086</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AI0084</t>
+          <t>AI0087</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AI0085</t>
+          <t>AI0088</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AI0086</t>
+          <t>AI0089</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
